--- a/output/pdf_financials_xlsx/AIV.P.xlsx
+++ b/output/pdf_financials_xlsx/AIV.P.xlsx
@@ -672,16 +672,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014205</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.053126</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.045774</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.034149</v>
       </c>
     </row>
     <row r="13">
@@ -1032,16 +1032,16 @@
         <v>-0.224472</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.03085</v>
+        <v>-0.045055</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.037325</v>
+        <v>-0.090451</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.051595</v>
+        <v>-0.097369</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.216294</v>
+        <v>0.182145</v>
       </c>
     </row>
     <row r="28">
@@ -1076,16 +1076,16 @@
         <v>-0.224472</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.03085</v>
+        <v>-0.045055</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.037325</v>
+        <v>-0.090451</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.051595</v>
+        <v>-0.097369</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.216294</v>
+        <v>0.182145</v>
       </c>
     </row>
     <row r="30">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
